--- a/business_surveys/019_women_golf_shorts_shopping_survey--business_surveys.xlsx
+++ b/business_surveys/019_women_golf_shorts_shopping_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>$40</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>$40</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>$40</t>
+          <t>000-$60</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>$40</t>
+          <t>000-$60</t>
         </is>
       </c>
     </row>
@@ -2567,12 +2567,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>000-$60</t>
+          <t>$60</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>000-$60</t>
+          <t>$60</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000-$80</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000-$80</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$80</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$80</t>
         </is>
       </c>
     </row>
@@ -2618,63 +2618,63 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>000-$80</t>
+          <t>000+</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>000-$80</t>
+          <t>000+</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_level_choices</t>
+          <t>shopping_channel_importance_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_level_choices</t>
+          <t>shopping_channel_importance_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_level_choices</t>
+          <t>shopping_channel_importance_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>000+</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>000+</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
@@ -2686,63 +2686,63 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>very_important</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Very Important</t>
+          <t>Not at All Important</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>shopping_channel_importance_choices</t>
+          <t>brand_loyalty_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>somewhat_important</t>
+          <t>very_loyal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Somewhat Important</t>
+          <t>Very Loyal</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>shopping_channel_importance_choices</t>
+          <t>brand_loyalty_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>not_very_important</t>
+          <t>somewhat_loyal</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Not Very Important</t>
+          <t>Somewhat Loyal</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>shopping_channel_importance_choices</t>
+          <t>brand_loyalty_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>not_at_all_important</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Not at All Important</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2754,148 +2754,148 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>very_loyal</t>
+          <t>not_at_all_loyal</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Very Loyal</t>
+          <t>Not at All Loyal</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>brand_loyalty_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>somewhat_loyal</t>
+          <t>very_frequently</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Somewhat Loyal</t>
+          <t>Very Frequently</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>brand_loyalty_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_frequently</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Frequently</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>brand_loyalty_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>somewhat_loyal</t>
+          <t>not_very_frequently</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Somewhat Loyal</t>
+          <t>Not Very Frequently</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>brand_loyalty_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>not_at_all_loyal</t>
+          <t>not_at_all_frequently</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Not at All Loyal</t>
+          <t>Not at All Frequently</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>purchase_satisfaction_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>very_frequently</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Very Frequently</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>purchase_satisfaction_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>somewhat_frequently</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Somewhat Frequently</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>purchase_satisfaction_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>not_very_frequently</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Not Very Frequently</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>purchase_satisfaction_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>not_at_all_frequently</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Not at All Frequently</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2907,80 +2907,80 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>purchase_satisfaction_choices</t>
+          <t>purchase_confidence_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Very Confident</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>purchase_satisfaction_choices</t>
+          <t>purchase_confidence_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Confident</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>purchase_satisfaction_choices</t>
+          <t>purchase_confidence_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>purchase_satisfaction_choices</t>
+          <t>purchase_confidence_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>somewhat_insecure</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Somewhat Insecure</t>
         </is>
       </c>
     </row>
@@ -2992,80 +2992,80 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>very_confident</t>
+          <t>very_insecure</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Very Confident</t>
+          <t>Very Insecure</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>purchase_confidence_choices</t>
+          <t>purchase_habits_instore_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>somewhat_confident</t>
+          <t>try_before_you_buy</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Somewhat Confident</t>
+          <t>Try Before You Buy</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>purchase_confidence_choices</t>
+          <t>purchase_habits_instore_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>online_research</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Online Research</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>purchase_confidence_choices</t>
+          <t>purchase_habits_instore_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>somewhat_insecure</t>
+          <t>buy_on_impulse</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Somewhat Insecure</t>
+          <t>Buy on Impulse</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>purchase_confidence_choices</t>
+          <t>purchase_habits_instore_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>very_insecure</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Very Insecure</t>
+          <t>Recommendation</t>
         </is>
       </c>
     </row>
@@ -3077,80 +3077,80 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>try_before_you_buy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Try Before You Buy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>purchase_habits_instore_choices</t>
+          <t>purchase_habits_online_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>online_research</t>
+          <t>try_before_you_buy</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Online Research</t>
+          <t>Try Before You Buy</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>purchase_habits_instore_choices</t>
+          <t>purchase_habits_online_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>buy_on_impulse</t>
+          <t>online_research</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Buy on Impulse</t>
+          <t>Online Research</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>purchase_habits_instore_choices</t>
+          <t>purchase_habits_online_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>buy_on_impulse</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>Buy on Impulse</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>purchase_habits_instore_choices</t>
+          <t>purchase_habits_online_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Recommendation</t>
         </is>
       </c>
     </row>
@@ -3162,78 +3162,10 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>try_before_you_buy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
-        <is>
-          <t>Try Before You Buy</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>purchase_habits_online_choices</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>online_research</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Online Research</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>purchase_habits_online_choices</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>buy_on_impulse</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Buy on Impulse</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>purchase_habits_online_choices</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>purchase_habits_online_choices</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
